--- a/exports/red5-dhcp_lighting.xlsx
+++ b/exports/red5-dhcp_lighting.xlsx
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-27  ·  source: generate_io_list.py</t>
+          <t>Generated 2026-07-30  ·  source: generate_io_list.py</t>
         </is>
       </c>
     </row>

--- a/exports/red5-dhcp_lighting.xlsx
+++ b/exports/red5-dhcp_lighting.xlsx
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated 2026-07-30  ·  source: generate_io_list.py</t>
+          <t>Generated 2026-08-03  ·  source: generate_io_list.py</t>
         </is>
       </c>
     </row>
